--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0005.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0005.xlsx
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
